--- a/output/pdf_financials_xlsx/FUTR.xlsx
+++ b/output/pdf_financials_xlsx/FUTR.xlsx
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.288485</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.601815</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.564868</v>
       </c>
     </row>
     <row r="93">
@@ -2996,7 +2996,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -3025,7 +3029,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3384,7 +3392,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>2.288485</v>
       </c>

--- a/output/pdf_financials_xlsx/FUTR.xlsx
+++ b/output/pdf_financials_xlsx/FUTR.xlsx
@@ -580,10 +580,10 @@
         <v>0.269112</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.076293</v>
+        <v>0.571305</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.032238</v>
+        <v>0.308139</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>-0.571305</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.032238</v>
+        <v>-0.308139</v>
       </c>
     </row>
     <row r="12">
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002232</v>
       </c>
     </row>
     <row r="13">
@@ -885,7 +885,7 @@
         <v>-1.686822</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.686822</v>
+        <v>-1.689054</v>
       </c>
     </row>
     <row r="28">
@@ -917,7 +917,7 @@
         <v>-1.686822</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.686822</v>
+        <v>-1.689054</v>
       </c>
     </row>
     <row r="30">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.067117</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000855</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001504</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.067117</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000855</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001504</v>
       </c>
     </row>
     <row r="37">
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.125193</v>
+        <v>0.058076</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.045211</v>
+        <v>0.044356</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">

--- a/output/pdf_financials_xlsx/FUTR.xlsx
+++ b/output/pdf_financials_xlsx/FUTR.xlsx
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.303774</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.400064</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.222871</v>
       </c>
     </row>
     <row r="65">
